--- a/survey_templates/041_learning_motivation_during_hybrid_classes_survey--survey_templates.xlsx
+++ b/survey_templates/041_learning_motivation_during_hybrid_classes_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option22</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option22</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option23</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option23</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option24</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option24</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option25</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option25</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option26</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option26</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option27</t>
+          <t>option_27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option27</t>
+          <t>Option 27</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option28</t>
+          <t>option_28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option28</t>
+          <t>Option 28</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option29</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option29</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option30</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option30</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
